--- a/Bibsam_tidskriftslistor/scifree_data_plos.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_plos.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_0B8D1EA7C1DC08CAAAF444D927E7599B0B2A310B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16D77287-40AB-4F9E-B220-F121D219D03C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8080C7AB-6FE7-410F-928D-A911B8E231ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -176,6 +176,24 @@
   </si>
   <si>
     <t>https://journals.plos.org/complexsystems/</t>
+  </si>
+  <si>
+    <t>3070-801X</t>
+  </si>
+  <si>
+    <t>PLOS Aging and Health</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/agingandhealth/</t>
+  </si>
+  <si>
+    <t>3070-8141</t>
+  </si>
+  <si>
+    <t>PLOS Ecosystems</t>
+  </si>
+  <si>
+    <t>https://journals.plos.org/ecosystems/</t>
   </si>
 </sst>
 </file>
@@ -231,10 +249,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4828232-EA87-49EB-85C0-E7FBA168EFED}" name="Table2" displayName="Table2" ref="A1:G15" totalsRowShown="0">
-  <autoFilter ref="A1:G15" xr:uid="{A4828232-EA87-49EB-85C0-E7FBA168EFED}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G15">
-    <sortCondition ref="D1:D15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4828232-EA87-49EB-85C0-E7FBA168EFED}" name="Table2" displayName="Table2" ref="A1:G17" totalsRowShown="0">
+  <autoFilter ref="A1:G17" xr:uid="{A4828232-EA87-49EB-85C0-E7FBA168EFED}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
+    <sortCondition ref="D1:D17"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{5883B40B-D2FA-4B61-AFC0-1E339F3BBB9D}" name="Imprint"/>
@@ -512,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B544400-77B7-435C-ADD7-DE93BA806E78}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -552,13 +570,13 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
         <v>21</v>
@@ -572,13 +590,13 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
@@ -592,13 +610,13 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
         <v>21</v>
@@ -612,13 +630,13 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="F5" t="s">
         <v>21</v>
@@ -632,13 +650,13 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
         <v>21</v>
@@ -652,13 +670,13 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
         <v>21</v>
@@ -672,13 +690,13 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
         <v>21</v>
@@ -692,13 +710,13 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -712,13 +730,13 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F10" t="s">
         <v>21</v>
@@ -732,13 +750,13 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
         <v>21</v>
@@ -752,13 +770,13 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -772,13 +790,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -792,13 +810,13 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
         <v>21</v>
@@ -812,18 +830,58 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
         <v>45</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D17" t="s">
         <v>19</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E17" t="s">
         <v>41</v>
       </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
         <v>7</v>
       </c>
     </row>
